--- a/artfynd/A 8723-2025 artfynd.xlsx
+++ b/artfynd/A 8723-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127832365</v>
+        <v>127826580</v>
       </c>
       <c r="B2" t="n">
-        <v>80159</v>
+        <v>79023</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>644676</v>
+        <v>644560</v>
       </c>
       <c r="R2" t="n">
-        <v>7134257</v>
+        <v>7134338</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127826580</v>
+        <v>127832365</v>
       </c>
       <c r="B3" t="n">
-        <v>79020</v>
+        <v>80162</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>644560</v>
+        <v>644676</v>
       </c>
       <c r="R3" t="n">
-        <v>7134338</v>
+        <v>7134257</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127832479</v>
+        <v>127830667</v>
       </c>
       <c r="B4" t="n">
-        <v>80123</v>
+        <v>80161</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>644594</v>
+        <v>644758</v>
       </c>
       <c r="R4" t="n">
-        <v>7134389</v>
+        <v>7134162</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127830667</v>
+        <v>127832479</v>
       </c>
       <c r="B5" t="n">
-        <v>80158</v>
+        <v>80126</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>644758</v>
+        <v>644594</v>
       </c>
       <c r="R5" t="n">
-        <v>7134162</v>
+        <v>7134389</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
         <v>127830661</v>
       </c>
       <c r="B6" t="n">
-        <v>80152</v>
+        <v>80155</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>127832353</v>
       </c>
       <c r="B7" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>127832397</v>
       </c>
       <c r="B8" t="n">
-        <v>80152</v>
+        <v>80155</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>127829128</v>
       </c>
       <c r="B9" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>127827815</v>
       </c>
       <c r="B10" t="n">
-        <v>80152</v>
+        <v>80155</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127826599</v>
+        <v>127831265</v>
       </c>
       <c r="B11" t="n">
-        <v>75144</v>
+        <v>80126</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>644555</v>
+        <v>644735</v>
       </c>
       <c r="R11" t="n">
-        <v>7134341</v>
+        <v>7134263</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127831265</v>
+        <v>127826599</v>
       </c>
       <c r="B12" t="n">
-        <v>80123</v>
+        <v>75147</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>644735</v>
+        <v>644555</v>
       </c>
       <c r="R12" t="n">
-        <v>7134263</v>
+        <v>7134341</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 8723-2025 artfynd.xlsx
+++ b/artfynd/A 8723-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127826580</v>
+        <v>127832365</v>
       </c>
       <c r="B2" t="n">
-        <v>79023</v>
+        <v>80168</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>644560</v>
+        <v>644676</v>
       </c>
       <c r="R2" t="n">
-        <v>7134338</v>
+        <v>7134257</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127832365</v>
+        <v>127826580</v>
       </c>
       <c r="B3" t="n">
-        <v>80162</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>644676</v>
+        <v>644560</v>
       </c>
       <c r="R3" t="n">
-        <v>7134257</v>
+        <v>7134338</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127830667</v>
+        <v>127832479</v>
       </c>
       <c r="B4" t="n">
-        <v>80161</v>
+        <v>80132</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>644758</v>
+        <v>644594</v>
       </c>
       <c r="R4" t="n">
-        <v>7134162</v>
+        <v>7134389</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127832479</v>
+        <v>127830667</v>
       </c>
       <c r="B5" t="n">
-        <v>80126</v>
+        <v>80167</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>644594</v>
+        <v>644758</v>
       </c>
       <c r="R5" t="n">
-        <v>7134389</v>
+        <v>7134162</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
         <v>127830661</v>
       </c>
       <c r="B6" t="n">
-        <v>80155</v>
+        <v>80161</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>127832353</v>
       </c>
       <c r="B7" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>127832397</v>
       </c>
       <c r="B8" t="n">
-        <v>80155</v>
+        <v>80161</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>127829128</v>
       </c>
       <c r="B9" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>127827815</v>
       </c>
       <c r="B10" t="n">
-        <v>80155</v>
+        <v>80161</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>127831265</v>
       </c>
       <c r="B11" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>127826599</v>
       </c>
       <c r="B12" t="n">
-        <v>75147</v>
+        <v>75153</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 8723-2025 artfynd.xlsx
+++ b/artfynd/A 8723-2025 artfynd.xlsx
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127832397</v>
+        <v>127829128</v>
       </c>
       <c r="B8" t="n">
-        <v>80161</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>644694</v>
+        <v>644715</v>
       </c>
       <c r="R8" t="n">
-        <v>7134217</v>
+        <v>7134130</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127829128</v>
+        <v>127832397</v>
       </c>
       <c r="B9" t="n">
-        <v>79029</v>
+        <v>80161</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>644715</v>
+        <v>644694</v>
       </c>
       <c r="R9" t="n">
-        <v>7134130</v>
+        <v>7134217</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 8723-2025 artfynd.xlsx
+++ b/artfynd/A 8723-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127832365</v>
+        <v>127826580</v>
       </c>
       <c r="B2" t="n">
-        <v>80168</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>644676</v>
+        <v>644560</v>
       </c>
       <c r="R2" t="n">
-        <v>7134257</v>
+        <v>7134338</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127826580</v>
+        <v>127832365</v>
       </c>
       <c r="B3" t="n">
-        <v>79029</v>
+        <v>80168</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>644560</v>
+        <v>644676</v>
       </c>
       <c r="R3" t="n">
-        <v>7134338</v>
+        <v>7134257</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 8723-2025 artfynd.xlsx
+++ b/artfynd/A 8723-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127826580</v>
+        <v>127832365</v>
       </c>
       <c r="B2" t="n">
-        <v>79029</v>
+        <v>80168</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>644560</v>
+        <v>644676</v>
       </c>
       <c r="R2" t="n">
-        <v>7134338</v>
+        <v>7134257</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127832365</v>
+        <v>127826580</v>
       </c>
       <c r="B3" t="n">
-        <v>80168</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>644676</v>
+        <v>644560</v>
       </c>
       <c r="R3" t="n">
-        <v>7134257</v>
+        <v>7134338</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127831265</v>
+        <v>127826599</v>
       </c>
       <c r="B11" t="n">
-        <v>80132</v>
+        <v>75153</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>644735</v>
+        <v>644555</v>
       </c>
       <c r="R11" t="n">
-        <v>7134263</v>
+        <v>7134341</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127826599</v>
+        <v>127831265</v>
       </c>
       <c r="B12" t="n">
-        <v>75153</v>
+        <v>80132</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>644555</v>
+        <v>644735</v>
       </c>
       <c r="R12" t="n">
-        <v>7134341</v>
+        <v>7134263</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 8723-2025 artfynd.xlsx
+++ b/artfynd/A 8723-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127826580</v>
+        <v>127832365</v>
       </c>
       <c r="B2" t="n">
-        <v>79029</v>
+        <v>80168</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>644560</v>
+        <v>644676</v>
       </c>
       <c r="R2" t="n">
-        <v>7134338</v>
+        <v>7134257</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127832365</v>
+        <v>127826580</v>
       </c>
       <c r="B3" t="n">
-        <v>80168</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>644676</v>
+        <v>644560</v>
       </c>
       <c r="R3" t="n">
-        <v>7134257</v>
+        <v>7134338</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 8723-2025 artfynd.xlsx
+++ b/artfynd/A 8723-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127832365</v>
       </c>
       <c r="B2" t="n">
-        <v>80168</v>
+        <v>80171</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127826580</v>
       </c>
       <c r="B3" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127832479</v>
       </c>
       <c r="B4" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127830667</v>
       </c>
       <c r="B5" t="n">
-        <v>80167</v>
+        <v>80170</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127830661</v>
       </c>
       <c r="B6" t="n">
-        <v>80161</v>
+        <v>80164</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>127832353</v>
       </c>
       <c r="B7" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>127829128</v>
       </c>
       <c r="B8" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>127832397</v>
       </c>
       <c r="B9" t="n">
-        <v>80161</v>
+        <v>80164</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>127827815</v>
       </c>
       <c r="B10" t="n">
-        <v>80161</v>
+        <v>80164</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127826599</v>
+        <v>127831265</v>
       </c>
       <c r="B11" t="n">
-        <v>75153</v>
+        <v>80135</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>644555</v>
+        <v>644735</v>
       </c>
       <c r="R11" t="n">
-        <v>7134341</v>
+        <v>7134263</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127831265</v>
+        <v>127826599</v>
       </c>
       <c r="B12" t="n">
-        <v>80132</v>
+        <v>75156</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>644735</v>
+        <v>644555</v>
       </c>
       <c r="R12" t="n">
-        <v>7134263</v>
+        <v>7134341</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 8723-2025 artfynd.xlsx
+++ b/artfynd/A 8723-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127832365</v>
       </c>
       <c r="B2" t="n">
-        <v>80171</v>
+        <v>80224</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127826580</v>
       </c>
       <c r="B3" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127832479</v>
       </c>
       <c r="B4" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127830667</v>
       </c>
       <c r="B5" t="n">
-        <v>80170</v>
+        <v>80223</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127830661</v>
       </c>
       <c r="B6" t="n">
-        <v>80164</v>
+        <v>80217</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>127832353</v>
       </c>
       <c r="B7" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>127829128</v>
       </c>
       <c r="B8" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>127832397</v>
       </c>
       <c r="B9" t="n">
-        <v>80164</v>
+        <v>80217</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>127827815</v>
       </c>
       <c r="B10" t="n">
-        <v>80164</v>
+        <v>80217</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>127831265</v>
       </c>
       <c r="B11" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>127826599</v>
       </c>
       <c r="B12" t="n">
-        <v>75156</v>
+        <v>75171</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 8723-2025 artfynd.xlsx
+++ b/artfynd/A 8723-2025 artfynd.xlsx
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127832479</v>
+        <v>127830667</v>
       </c>
       <c r="B4" t="n">
-        <v>80188</v>
+        <v>80223</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>644594</v>
+        <v>644758</v>
       </c>
       <c r="R4" t="n">
-        <v>7134389</v>
+        <v>7134162</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127830667</v>
+        <v>127832479</v>
       </c>
       <c r="B5" t="n">
-        <v>80223</v>
+        <v>80188</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>644758</v>
+        <v>644594</v>
       </c>
       <c r="R5" t="n">
-        <v>7134162</v>
+        <v>7134389</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1257,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127829128</v>
+        <v>127832397</v>
       </c>
       <c r="B8" t="n">
-        <v>79083</v>
+        <v>80217</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>644715</v>
+        <v>644694</v>
       </c>
       <c r="R8" t="n">
-        <v>7134130</v>
+        <v>7134217</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127832397</v>
+        <v>127829128</v>
       </c>
       <c r="B9" t="n">
-        <v>80217</v>
+        <v>79083</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>644694</v>
+        <v>644715</v>
       </c>
       <c r="R9" t="n">
-        <v>7134217</v>
+        <v>7134130</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127831265</v>
+        <v>127826599</v>
       </c>
       <c r="B11" t="n">
-        <v>80188</v>
+        <v>75171</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>644735</v>
+        <v>644555</v>
       </c>
       <c r="R11" t="n">
-        <v>7134263</v>
+        <v>7134341</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127826599</v>
+        <v>127831265</v>
       </c>
       <c r="B12" t="n">
-        <v>75171</v>
+        <v>80188</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>644555</v>
+        <v>644735</v>
       </c>
       <c r="R12" t="n">
-        <v>7134341</v>
+        <v>7134263</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 8723-2025 artfynd.xlsx
+++ b/artfynd/A 8723-2025 artfynd.xlsx
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127826599</v>
+        <v>127831265</v>
       </c>
       <c r="B11" t="n">
-        <v>75171</v>
+        <v>80188</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>644555</v>
+        <v>644735</v>
       </c>
       <c r="R11" t="n">
-        <v>7134341</v>
+        <v>7134263</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127831265</v>
+        <v>127826599</v>
       </c>
       <c r="B12" t="n">
-        <v>80188</v>
+        <v>75171</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>644735</v>
+        <v>644555</v>
       </c>
       <c r="R12" t="n">
-        <v>7134263</v>
+        <v>7134341</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 8723-2025 artfynd.xlsx
+++ b/artfynd/A 8723-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,45 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127832365</v>
+        <v>16839678</v>
       </c>
       <c r="B2" t="n">
-        <v>80224</v>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lill-Hundberget, Lill-Hundberget, Ås lm</t>
+          <t>Lill-Hundberget, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>644676</v>
+        <v>644708</v>
       </c>
       <c r="R2" t="n">
-        <v>7134257</v>
+        <v>7134380</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2014-08-11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2014-08-11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -756,16 +756,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Blanskog med gran och björk</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Herman Niva</t>
+          <t>Sofia Lundman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Herman Niva</t>
+          <t>Sofia Lundman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -775,11 +785,11 @@
         <v>127826580</v>
       </c>
       <c r="B3" t="n">
-        <v>79083</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -869,27 +879,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127830667</v>
+        <v>127829128</v>
       </c>
       <c r="B4" t="n">
-        <v>80223</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -904,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>644758</v>
+        <v>644715</v>
       </c>
       <c r="R4" t="n">
-        <v>7134162</v>
+        <v>7134130</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127832479</v>
+        <v>127826599</v>
       </c>
       <c r="B5" t="n">
-        <v>80188</v>
+        <v>83307</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +987,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>644594</v>
+        <v>644555</v>
       </c>
       <c r="R5" t="n">
-        <v>7134389</v>
+        <v>7134341</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1073,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127830661</v>
+        <v>127831265</v>
       </c>
       <c r="B6" t="n">
-        <v>80217</v>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>644755</v>
+        <v>644735</v>
       </c>
       <c r="R6" t="n">
-        <v>7134165</v>
+        <v>7134263</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,7 +1173,7 @@
         <v>127832353</v>
       </c>
       <c r="B7" t="n">
-        <v>80188</v>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1257,32 +1267,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127832397</v>
+        <v>127832479</v>
       </c>
       <c r="B8" t="n">
-        <v>80217</v>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>644694</v>
+        <v>644594</v>
       </c>
       <c r="R8" t="n">
-        <v>7134217</v>
+        <v>7134389</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,32 +1364,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127829128</v>
+        <v>127827815</v>
       </c>
       <c r="B9" t="n">
-        <v>79083</v>
+        <v>80461</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>644715</v>
+        <v>644644</v>
       </c>
       <c r="R9" t="n">
-        <v>7134130</v>
+        <v>7134225</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127827815</v>
+        <v>127830661</v>
       </c>
       <c r="B10" t="n">
-        <v>80217</v>
+        <v>80461</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1486,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>644644</v>
+        <v>644755</v>
       </c>
       <c r="R10" t="n">
-        <v>7134225</v>
+        <v>7134165</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,32 +1558,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127831265</v>
+        <v>127832397</v>
       </c>
       <c r="B11" t="n">
-        <v>80188</v>
+        <v>80461</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>644735</v>
+        <v>644694</v>
       </c>
       <c r="R11" t="n">
-        <v>7134263</v>
+        <v>7134217</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,32 +1655,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127826599</v>
+        <v>127830667</v>
       </c>
       <c r="B12" t="n">
-        <v>75171</v>
+        <v>80467</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>6463</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>644555</v>
+        <v>644758</v>
       </c>
       <c r="R12" t="n">
-        <v>7134341</v>
+        <v>7134162</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1739,6 +1749,103 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>127832365</v>
+      </c>
+      <c r="B13" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lill-Hundberget, Lill-Hundberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>644676</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7134257</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8723-2025 artfynd.xlsx
+++ b/artfynd/A 8723-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>16839678</v>
+        <v>135235703</v>
       </c>
       <c r="B2" t="n">
-        <v>80433</v>
+        <v>89354</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lill-Hundberget, Ås lm</t>
+          <t>Lillhundberget, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>644708</v>
+        <v>644703</v>
       </c>
       <c r="R2" t="n">
-        <v>7134380</v>
+        <v>7134417</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2014-08-11</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2014-08-11</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -756,71 +756,65 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Blanskog med gran och björk</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sofia Lundman</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sofia Lundman</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127826580</v>
+        <v>16839678</v>
       </c>
       <c r="B3" t="n">
-        <v>79327</v>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lill-Hundberget, Lill-Hundberget, Ås lm</t>
+          <t>Lill-Hundberget, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>644560</v>
+        <v>644708</v>
       </c>
       <c r="R3" t="n">
-        <v>7134338</v>
+        <v>7134380</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,12 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2014-08-11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2014-08-11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -863,61 +857,71 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Blanskog med gran och björk</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Herman Niva</t>
+          <t>Sofia Lundman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Herman Niva</t>
+          <t>Sofia Lundman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127829128</v>
+        <v>135236002</v>
       </c>
       <c r="B4" t="n">
-        <v>79327</v>
+        <v>80489</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lill-Hundberget, Lill-Hundberget, Ås lm</t>
+          <t>Lillhundberget, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>644715</v>
+        <v>644727</v>
       </c>
       <c r="R4" t="n">
-        <v>7134130</v>
+        <v>7134242</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -944,12 +948,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -964,44 +968,48 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Herman Niva</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Herman Niva</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127826599</v>
+        <v>127826580</v>
       </c>
       <c r="B5" t="n">
-        <v>83307</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1019,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>644555</v>
+        <v>644560</v>
       </c>
       <c r="R5" t="n">
-        <v>7134341</v>
+        <v>7134338</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,32 +1081,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127831265</v>
+        <v>127829128</v>
       </c>
       <c r="B6" t="n">
-        <v>80432</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1116,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>644735</v>
+        <v>644715</v>
       </c>
       <c r="R6" t="n">
-        <v>7134263</v>
+        <v>7134130</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,45 +1178,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127832353</v>
+        <v>135235704</v>
       </c>
       <c r="B7" t="n">
-        <v>80432</v>
+        <v>79373</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lill-Hundberget, Lill-Hundberget, Ås lm</t>
+          <t>Lillhundberget, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>644673</v>
+        <v>644771</v>
       </c>
       <c r="R7" t="n">
-        <v>7134259</v>
+        <v>7134137</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1235,12 +1243,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1255,57 +1263,61 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Herman Niva</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Herman Niva</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127832479</v>
+        <v>135235705</v>
       </c>
       <c r="B8" t="n">
-        <v>80432</v>
+        <v>79373</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lill-Hundberget, Lill-Hundberget, Ås lm</t>
+          <t>Lillhundberget, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>644594</v>
+        <v>644782</v>
       </c>
       <c r="R8" t="n">
-        <v>7134389</v>
+        <v>7134094</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1332,12 +1344,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1352,57 +1364,61 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Herman Niva</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Herman Niva</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127827815</v>
+        <v>135236003</v>
       </c>
       <c r="B9" t="n">
-        <v>80461</v>
+        <v>79373</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lill-Hundberget, Lill-Hundberget, Ås lm</t>
+          <t>Lillhundberget, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>644644</v>
+        <v>644730</v>
       </c>
       <c r="R9" t="n">
-        <v>7134225</v>
+        <v>7134217</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1429,12 +1445,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1449,44 +1465,48 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Herman Niva</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Herman Niva</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127830661</v>
+        <v>127826599</v>
       </c>
       <c r="B10" t="n">
-        <v>80461</v>
+        <v>83307</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1516,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>644755</v>
+        <v>644555</v>
       </c>
       <c r="R10" t="n">
-        <v>7134165</v>
+        <v>7134341</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1558,32 +1578,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127832397</v>
+        <v>127831265</v>
       </c>
       <c r="B11" t="n">
-        <v>80461</v>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,10 +1613,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>644694</v>
+        <v>644735</v>
       </c>
       <c r="R11" t="n">
-        <v>7134217</v>
+        <v>7134263</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1655,32 +1675,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127830667</v>
+        <v>127832353</v>
       </c>
       <c r="B12" t="n">
-        <v>80467</v>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1710,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>644758</v>
+        <v>644673</v>
       </c>
       <c r="R12" t="n">
-        <v>7134162</v>
+        <v>7134259</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1752,32 +1772,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127832365</v>
+        <v>127832479</v>
       </c>
       <c r="B13" t="n">
-        <v>80468</v>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1807,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>644676</v>
+        <v>644594</v>
       </c>
       <c r="R13" t="n">
-        <v>7134257</v>
+        <v>7134389</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1846,6 +1866,491 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>127827815</v>
+      </c>
+      <c r="B14" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Lill-Hundberget, Lill-Hundberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>644644</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7134225</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>127830661</v>
+      </c>
+      <c r="B15" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Lill-Hundberget, Lill-Hundberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>644755</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7134165</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>127832397</v>
+      </c>
+      <c r="B16" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Lill-Hundberget, Lill-Hundberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>644694</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7134217</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>127830667</v>
+      </c>
+      <c r="B17" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Lill-Hundberget, Lill-Hundberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>644758</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7134162</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>127832365</v>
+      </c>
+      <c r="B18" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Lill-Hundberget, Lill-Hundberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>644676</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7134257</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8723-2025 artfynd.xlsx
+++ b/artfynd/A 8723-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135235703</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16839678</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -981,6 +996,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135236002</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1078,6 +1098,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127826580</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1175,6 +1200,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127829128</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1276,6 +1306,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135235704</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1377,6 +1412,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135235705</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1478,6 +1518,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135236003</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1575,6 +1620,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127826599</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1672,6 +1722,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127831265</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1769,6 +1824,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127832353</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1866,6 +1926,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127832479</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1963,6 +2028,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127827815</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2060,6 +2130,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127830661</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2157,6 +2232,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127832397</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2254,6 +2334,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127830667</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2351,8 +2436,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127832365</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 8723-2025 artfynd.xlsx
+++ b/artfynd/A 8723-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135235703</v>
       </c>
       <c r="B2" t="n">
-        <v>89354</v>
+        <v>89396</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>135236002</v>
       </c>
       <c r="B4" t="n">
-        <v>80489</v>
+        <v>80527</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         <v>135235704</v>
       </c>
       <c r="B7" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>135235705</v>
       </c>
       <c r="B8" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>135236003</v>
       </c>
       <c r="B9" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 8723-2025 artfynd.xlsx
+++ b/artfynd/A 8723-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135235703</v>
       </c>
       <c r="B2" t="n">
-        <v>89396</v>
+        <v>89423</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>135236002</v>
       </c>
       <c r="B4" t="n">
-        <v>80527</v>
+        <v>80554</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         <v>135235704</v>
       </c>
       <c r="B7" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>135235705</v>
       </c>
       <c r="B8" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>135236003</v>
       </c>
       <c r="B9" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 8723-2025 artfynd.xlsx
+++ b/artfynd/A 8723-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ13"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>16839678</v>
+        <v>135235703</v>
       </c>
       <c r="B2" t="n">
-        <v>80433</v>
+        <v>89426</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lill-Hundberget, Ås lm</t>
+          <t>Lillhundberget, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>644708</v>
+        <v>644703</v>
       </c>
       <c r="R2" t="n">
-        <v>7134380</v>
+        <v>7134417</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2014-08-11</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2014-08-11</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -761,76 +761,70 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Blanskog med gran och björk</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sofia Lundman</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sofia Lundman</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16839678</t>
+          <t>https://artportalen.se/Sighting/135235703</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127826580</v>
+        <v>16839678</v>
       </c>
       <c r="B3" t="n">
-        <v>79327</v>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lill-Hundberget, Lill-Hundberget, Ås lm</t>
+          <t>Lill-Hundberget, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>644560</v>
+        <v>644708</v>
       </c>
       <c r="R3" t="n">
-        <v>7134338</v>
+        <v>7134380</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,12 +851,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2014-08-11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2014-08-11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -873,66 +867,76 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Blanskog med gran och björk</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Herman Niva</t>
+          <t>Sofia Lundman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Herman Niva</t>
+          <t>Sofia Lundman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127826580</t>
+          <t>https://artportalen.se/Sighting/16839678</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127829128</v>
+        <v>135236002</v>
       </c>
       <c r="B4" t="n">
-        <v>79327</v>
+        <v>80557</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lill-Hundberget, Lill-Hundberget, Ås lm</t>
+          <t>Lillhundberget, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>644715</v>
+        <v>644727</v>
       </c>
       <c r="R4" t="n">
-        <v>7134130</v>
+        <v>7134242</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,12 +963,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,49 +983,53 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Herman Niva</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Herman Niva</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127829128</t>
+          <t>https://artportalen.se/Sighting/135236002</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127826599</v>
+        <v>127826580</v>
       </c>
       <c r="B5" t="n">
-        <v>83307</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>644555</v>
+        <v>644560</v>
       </c>
       <c r="R5" t="n">
-        <v>7134341</v>
+        <v>7134338</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,38 +1100,38 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127826599</t>
+          <t>https://artportalen.se/Sighting/127826580</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127831265</v>
+        <v>127829128</v>
       </c>
       <c r="B6" t="n">
-        <v>80432</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>644735</v>
+        <v>644715</v>
       </c>
       <c r="R6" t="n">
-        <v>7134263</v>
+        <v>7134130</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,51 +1202,51 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127831265</t>
+          <t>https://artportalen.se/Sighting/127829128</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127832353</v>
+        <v>135235704</v>
       </c>
       <c r="B7" t="n">
-        <v>80432</v>
+        <v>79441</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lill-Hundberget, Lill-Hundberget, Ås lm</t>
+          <t>Lillhundberget, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>644673</v>
+        <v>644771</v>
       </c>
       <c r="R7" t="n">
-        <v>7134259</v>
+        <v>7134137</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1265,12 +1273,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1285,62 +1293,66 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Herman Niva</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Herman Niva</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127832353</t>
+          <t>https://artportalen.se/Sighting/135235704</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127832479</v>
+        <v>135235705</v>
       </c>
       <c r="B8" t="n">
-        <v>80432</v>
+        <v>79441</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lill-Hundberget, Lill-Hundberget, Ås lm</t>
+          <t>Lillhundberget, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>644594</v>
+        <v>644782</v>
       </c>
       <c r="R8" t="n">
-        <v>7134389</v>
+        <v>7134094</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1367,12 +1379,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1387,62 +1399,66 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Herman Niva</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Herman Niva</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127832479</t>
+          <t>https://artportalen.se/Sighting/135235705</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127827815</v>
+        <v>135236003</v>
       </c>
       <c r="B9" t="n">
-        <v>80461</v>
+        <v>79441</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lill-Hundberget, Lill-Hundberget, Ås lm</t>
+          <t>Lillhundberget, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>644644</v>
+        <v>644730</v>
       </c>
       <c r="R9" t="n">
-        <v>7134225</v>
+        <v>7134217</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1469,12 +1485,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1489,49 +1505,53 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Herman Niva</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Herman Niva</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127827815</t>
+          <t>https://artportalen.se/Sighting/135236003</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127830661</v>
+        <v>127826599</v>
       </c>
       <c r="B10" t="n">
-        <v>80461</v>
+        <v>83307</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>644755</v>
+        <v>644555</v>
       </c>
       <c r="R10" t="n">
-        <v>7134165</v>
+        <v>7134341</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1602,38 +1622,38 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127830661</t>
+          <t>https://artportalen.se/Sighting/127826599</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127832397</v>
+        <v>127831265</v>
       </c>
       <c r="B11" t="n">
-        <v>80461</v>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>644694</v>
+        <v>644735</v>
       </c>
       <c r="R11" t="n">
-        <v>7134217</v>
+        <v>7134263</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1704,38 +1724,38 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127832397</t>
+          <t>https://artportalen.se/Sighting/127831265</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127830667</v>
+        <v>127832353</v>
       </c>
       <c r="B12" t="n">
-        <v>80467</v>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,10 +1765,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>644758</v>
+        <v>644673</v>
       </c>
       <c r="R12" t="n">
-        <v>7134162</v>
+        <v>7134259</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1806,38 +1826,38 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127830667</t>
+          <t>https://artportalen.se/Sighting/127832353</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127832365</v>
+        <v>127832479</v>
       </c>
       <c r="B13" t="n">
-        <v>80468</v>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1847,10 +1867,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>644676</v>
+        <v>644594</v>
       </c>
       <c r="R13" t="n">
-        <v>7134257</v>
+        <v>7134389</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1907,6 +1927,516 @@
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127832479</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>127827815</v>
+      </c>
+      <c r="B14" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Lill-Hundberget, Lill-Hundberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>644644</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7134225</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127827815</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>127830661</v>
+      </c>
+      <c r="B15" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Lill-Hundberget, Lill-Hundberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>644755</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7134165</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127830661</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>127832397</v>
+      </c>
+      <c r="B16" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Lill-Hundberget, Lill-Hundberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>644694</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7134217</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127832397</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>127830667</v>
+      </c>
+      <c r="B17" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Lill-Hundberget, Lill-Hundberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>644758</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7134162</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127830667</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>127832365</v>
+      </c>
+      <c r="B18" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Lill-Hundberget, Lill-Hundberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>644676</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7134257</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Herman Niva</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/127832365</t>
         </is>
@@ -1926,6 +2456,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 8723-2025 artfynd.xlsx
+++ b/artfynd/A 8723-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135235703</v>
       </c>
       <c r="B2" t="n">
-        <v>89426</v>
+        <v>89428</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
